--- a/data/감탄_합성데이터_v1.xlsx
+++ b/data/감탄_합성데이터_v1.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gamtan_synthetic_data_plan.md 합성데이터 제작 가이드 (2026-08-12 반입)</t>
+          <t>합성데이터_제작가이드.md 합성데이터 제작 가이드 (2026-08-12 반입)</t>
         </is>
       </c>
     </row>
